--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N93_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N93_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.44850250396328</v>
+        <v>4.785381656894033</v>
       </c>
       <c r="D2" t="n">
-        <v>29.74611525296612</v>
+        <v>4.833743728606995</v>
       </c>
       <c r="E2" t="n">
-        <v>7.70319701137439</v>
+        <v>1.251769514348338</v>
       </c>
       <c r="F2" t="n">
-        <v>6.91849829771385</v>
+        <v>1.1242559733785</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.84123758994527</v>
+        <v>3.061701108366106</v>
       </c>
       <c r="D3" t="n">
-        <v>19.13259248076933</v>
+        <v>3.109046278125016</v>
       </c>
       <c r="E3" t="n">
-        <v>7.70319701137439</v>
+        <v>1.251769514348338</v>
       </c>
       <c r="F3" t="n">
-        <v>6.91849829771385</v>
+        <v>1.1242559733785</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.65934551458137</v>
+        <v>6.119643646119473</v>
       </c>
       <c r="D4" t="n">
-        <v>35.88095056062762</v>
+        <v>5.830654466101989</v>
       </c>
       <c r="E4" t="n">
-        <v>7.70319701137439</v>
+        <v>1.251769514348338</v>
       </c>
       <c r="F4" t="n">
-        <v>6.91849829771385</v>
+        <v>1.1242559733785</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
